--- a/SampleLogging/1/student/CuongNHE186494/TC1/TC1_Result.xlsx
+++ b/SampleLogging/1/student/CuongNHE186494/TC1/TC1_Result.xlsx
@@ -91,7 +91,7 @@
     <x:t>CLIENT_INPUT</x:t>
   </x:si>
   <x:si>
-    <x:t>Sent input:  1, received response</x:t>
+    <x:t>Sent input: 1 + 2, received response</x:t>
   </x:si>
   <x:si>
     <x:t>USER-WAIT-3</x:t>
@@ -106,18 +106,12 @@
     <x:t>Text comparison passed: client output matches exactly</x:t>
   </x:si>
   <x:si>
-    <x:t>CLIENT-CONSOLE-3</x:t>
-  </x:si>
-  <x:si>
     <x:t>SERVER-CONSOLE-2</x:t>
   </x:si>
   <x:si>
     <x:t>Text comparison passed: server output matches exactly</x:t>
   </x:si>
   <x:si>
-    <x:t>SERVER-CONSOLE-3</x:t>
-  </x:si>
-  <x:si>
     <x:t>NETWORK-FLOW-3-1</x:t>
   </x:si>
   <x:si>
@@ -131,6 +125,12 @@
   </x:si>
   <x:si>
     <x:t>Network flow validation passed for packet 2: [SYN, ACK] Server-&gt;Client</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NETWORK-FLOW-3-3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Network flow validation passed for packet 3: [ACK] Client-&gt;Server</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -509,7 +509,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:F14"/>
+  <x:dimension ref="A1:F13"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="20.139196" style="0" customWidth="1"/>
@@ -557,7 +557,7 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>1320.038</x:v>
+        <x:v>1309.3709</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:6">
@@ -577,7 +577,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>1059.9577</x:v>
+        <x:v>6548.2704</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:6">
@@ -597,7 +597,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>0.0931</x:v>
+        <x:v>0.096</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:6">
@@ -617,7 +617,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="F5" s="0">
-        <x:v>508.4943</x:v>
+        <x:v>510.2754</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:6">
@@ -637,7 +637,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>1016.0487</x:v>
+        <x:v>1013.0689</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:6">
@@ -657,7 +657,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="F7" s="0">
-        <x:v>2121.8385</x:v>
+        <x:v>1127.726</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:6">
@@ -677,7 +677,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>1015.2133</x:v>
+        <x:v>1010.736</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:6">
@@ -697,7 +697,7 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="F9" s="0">
-        <x:v>4.7339</x:v>
+        <x:v>6.3669</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:6">
@@ -705,7 +705,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
         <x:v>28</x:v>
@@ -714,90 +714,70 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>0.4833</x:v>
+        <x:v>0.3003</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:6">
       <x:c r="A11" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C11" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D11" s="0" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>0.6893</x:v>
+        <x:v>1.8989</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:6">
       <x:c r="A12" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="C12" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D12" s="0" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>0.4015</x:v>
+        <x:v>0.168</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:6">
       <x:c r="A13" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="C13" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D13" s="0" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>2.7709</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:6">
-      <x:c r="A14" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="B14" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C14" s="0" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="D14" s="0" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E14" s="1" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="F14" s="0">
-        <x:v>0.1767</x:v>
+        <x:v>0.0652</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
